--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_278_R28.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_278_R28.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1245</v>
+        <v>2.7952</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1263</v>
+        <v>2.9651</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0019</v>
+        <v>-0.1699</v>
       </c>
       <c r="G2" t="n">
         <v>2.7061</v>
@@ -610,13 +610,13 @@
         <v>0.232</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3282</v>
+        <v>-0.0011</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1142</v>
+        <v>-0.047</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2139</v>
+        <v>0.0459</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1418</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8532</v>
+        <v>2.5917</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5515</v>
+        <v>4.0547</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6983</v>
+        <v>-1.4631</v>
       </c>
       <c r="G3" t="n">
         <v>3.6242</v>
@@ -688,13 +688,13 @@
         <v>0.6959</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.9307</v>
+        <v>-1.1923</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1949</v>
+        <v>-0.6917</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7358</v>
+        <v>-0.5006</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5361</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.155</v>
+        <v>1.4223</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1409</v>
+        <v>3.4082</v>
       </c>
       <c r="F4" t="n">
         <v>-1.9859</v>
@@ -766,10 +766,10 @@
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9946</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.187</v>
+        <v>-0.9197</v>
       </c>
       <c r="U4" t="n">
         <v>0.1924</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2166</v>
+        <v>-0.1419</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1195</v>
+        <v>0.1942</v>
       </c>
       <c r="F5" t="n">
         <v>-0.3361</v>
@@ -844,10 +844,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4639</v>
+        <v>-0.3892</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1494</v>
+        <v>-0.0747</v>
       </c>
       <c r="U5" t="n">
         <v>-0.3145</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7386</v>
+        <v>-0.5295</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0721</v>
+        <v>0.0026</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6665</v>
+        <v>-0.5321</v>
       </c>
       <c r="G6" t="n">
         <v>0.4578</v>
@@ -922,13 +922,13 @@
         <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3768</v>
+        <v>-1.1677</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5228</v>
+        <v>-0.4481</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.854</v>
+        <v>-0.7196</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2836</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6059</v>
+        <v>-1.2453</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3985</v>
+        <v>0.5911</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0044</v>
+        <v>-1.8364</v>
       </c>
       <c r="G7" t="n">
         <v>-0.7547</v>
@@ -1000,13 +1000,13 @@
         <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1734</v>
+        <v>-0.8127</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8883</v>
+        <v>-0.6956</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2851</v>
+        <v>-0.1171</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1418</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8332</v>
+        <v>-1.9026</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8656</v>
+        <v>0.897</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6988</v>
+        <v>-2.7996</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3125</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0154</v>
+        <v>-0.054</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4753</v>
+        <v>-0.4439</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4907</v>
+        <v>0.3899</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1017</v>
+        <v>-2.0344</v>
       </c>
       <c r="E9" t="n">
         <v>-0.6232</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4784</v>
+        <v>-1.4112</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3037</v>
@@ -1156,13 +1156,13 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7257</v>
+        <v>-0.6585</v>
       </c>
       <c r="T9" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.427</v>
+        <v>-0.3598</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5361</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7592</v>
+        <v>-3.9624</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6732</v>
+        <v>-0.4059</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.086</v>
+        <v>-3.5565</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5765</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4121</v>
+        <v>-0.6152</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0376</v>
+        <v>-0.7703</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6256</v>
+        <v>0.1551</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4665</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0524</v>
+        <v>-5.6518</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6487</v>
+        <v>-3.2817</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4037</v>
+        <v>-2.3701</v>
       </c>
       <c r="G11" t="n">
         <v>-5.7998</v>
@@ -1312,13 +1312,13 @@
         <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6752</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.311</v>
+        <v>-0.322</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3642</v>
+        <v>0.3978</v>
       </c>
       <c r="V11" t="n">
         <v>0.5361</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.5007</v>
+        <v>-6.8967</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.9656</v>
+        <v>-4.4624</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5351</v>
+        <v>-2.4343</v>
       </c>
       <c r="G12" t="n">
         <v>-4.5676</v>
@@ -1390,13 +1390,13 @@
         <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6469</v>
+        <v>-1.0429</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1949</v>
+        <v>-0.6917</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.452</v>
+        <v>-0.3512</v>
       </c>
       <c r="V12" t="n">
         <v>-1.7501</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.6756</v>
+        <v>-15.5554</v>
       </c>
       <c r="E13" t="n">
-        <v>2.219499999999998</v>
+        <v>3.339699999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-18.8951</v>
+        <v>-18.8952</v>
       </c>
       <c r="G13" t="n">
         <v>-4.879899999999999</v>
@@ -1468,13 +1468,13 @@
         <v>5.798999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.705299999999999</v>
+        <v>-6.585099999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.5237</v>
+        <v>-5.4034</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1816</v>
+        <v>-1.1817</v>
       </c>
       <c r="V13" t="n">
         <v>-5.250299999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.6096</v>
+        <v>8.4091</v>
       </c>
       <c r="E14" t="n">
-        <v>8.8528</v>
+        <v>6.9656</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7568</v>
+        <v>1.4435</v>
       </c>
       <c r="G14" t="n">
         <v>5.1582</v>
@@ -1546,13 +1546,13 @@
         <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>4.5415</v>
+        <v>2.341</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7799</v>
+        <v>0.8927</v>
       </c>
       <c r="U14" t="n">
-        <v>1.7616</v>
+        <v>1.4484</v>
       </c>
       <c r="V14" t="n">
         <v>0.6778999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.2538</v>
+        <v>6.7478</v>
       </c>
       <c r="E15" t="n">
-        <v>5.8733</v>
+        <v>6.1092</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3805</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>2.1351</v>
@@ -1624,13 +1624,13 @@
         <v>0.232</v>
       </c>
       <c r="S15" t="n">
-        <v>0.134</v>
+        <v>0.628</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4402</v>
+        <v>-0.2043</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5742</v>
+        <v>0.8323</v>
       </c>
       <c r="V15" t="n">
         <v>3.7527</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. CABOCLO</t>
+          <t>M. WRIGHT IV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5003</v>
+        <v>1.4497</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6895</v>
+        <v>1.6416</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1892</v>
+        <v>-0.192</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6718</v>
+        <v>0.2978</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3133</v>
+        <v>0.3279</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3585</v>
+        <v>-0.03</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3481</v>
+        <v>2.0815</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8822</v>
+        <v>0.7933</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4659</v>
+        <v>1.2882</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6762</v>
+        <v>-1.7837</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5688</v>
+        <v>-0.4655</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1074</v>
+        <v>-1.3182</v>
       </c>
       <c r="P16" t="n">
         <v>0.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="R16" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4573</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.13</v>
+        <v>-0.1177</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3273</v>
+        <v>1.0376</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.8608</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7886</v>
+        <v>0.1418</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. WRIGHT IV</t>
+          <t>B. CABOCLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4173</v>
+        <v>1.3487</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1698</v>
+        <v>3.5715</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-2.2228</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2978</v>
+        <v>2.6718</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3279</v>
+        <v>1.3133</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.03</v>
+        <v>1.3585</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0815</v>
+        <v>4.3481</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7933</v>
+        <v>1.8822</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2882</v>
+        <v>2.4659</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7837</v>
+        <v>-1.6762</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4655</v>
+        <v>-0.5688</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3182</v>
+        <v>-1.1074</v>
       </c>
       <c r="P17" t="n">
         <v>0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1125</v>
+        <v>0.3058</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5895</v>
+        <v>0.0121</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4771</v>
+        <v>0.2937</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.8608</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1418</v>
+        <v>-0.7886</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3751</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0067</v>
+        <v>2.5964</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6316</v>
+        <v>-1.7432</v>
       </c>
       <c r="G18" t="n">
         <v>0.4341</v>
@@ -1858,13 +1858,13 @@
         <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4771</v>
+        <v>0.9553</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2829</v>
+        <v>0.3068</v>
       </c>
       <c r="U18" t="n">
-        <v>0.76</v>
+        <v>0.6484</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5361</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0055</v>
+        <v>0.6117</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2158</v>
+        <v>0.6876</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2103</v>
+        <v>-0.0759</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0767</v>
@@ -1936,13 +1936,13 @@
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3664</v>
+        <v>0.2399</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4323</v>
+        <v>0.0395</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0659</v>
+        <v>0.2003</v>
       </c>
       <c r="V19" t="n">
         <v>2.1444</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ABASS</t>
+          <t>D. MUSA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0965</v>
+        <v>0.4589</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8617</v>
+        <v>1.1359</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7652</v>
+        <v>-0.677</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4703</v>
+        <v>-0.6539</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5067</v>
+        <v>-0.3326</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.977</v>
+        <v>-0.3213</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6455</v>
+        <v>1.1617</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0672</v>
+        <v>0.1113</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7127</v>
+        <v>1.0504</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1752</v>
+        <v>-1.8156</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4395</v>
+        <v>-0.4439</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2643</v>
+        <v>-1.3717</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3738</v>
+        <v>0.4865</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2161</v>
+        <v>-0.098</v>
       </c>
       <c r="U20" t="n">
-        <v>0.59</v>
+        <v>0.5845</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. MUSA</t>
+          <t>A. ABASS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2152</v>
+        <v>0.2402</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4282</v>
+        <v>-0.6257</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6434</v>
+        <v>0.866</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6539</v>
+        <v>-0.4703</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3326</v>
+        <v>0.5067</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3213</v>
+        <v>-0.977</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1617</v>
+        <v>-0.6455</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1113</v>
+        <v>0.0672</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0504</v>
+        <v>-0.7127</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8156</v>
+        <v>0.1752</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4439</v>
+        <v>0.4395</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3717</v>
+        <v>-0.2643</v>
       </c>
       <c r="P21" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1876</v>
+        <v>0.7106</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8057</v>
+        <v>0.0198</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6181</v>
+        <v>0.6908</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8411999999999999</v>
+        <v>-0.6504</v>
       </c>
       <c r="E22" t="n">
         <v>-2.1277</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2864</v>
+        <v>1.4773</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6805</v>
@@ -2170,13 +2170,13 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>1.017</v>
+        <v>1.2079</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1766</v>
       </c>
       <c r="U22" t="n">
-        <v>1.1936</v>
+        <v>1.3845</v>
       </c>
       <c r="V22" t="n">
         <v>0.6778999999999999</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3329</v>
+        <v>-2.007</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3516</v>
+        <v>-1.0593</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9813</v>
+        <v>-0.9477</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9359</v>
@@ -2248,13 +2248,13 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>1.3711</v>
+        <v>0.6969</v>
       </c>
       <c r="T23" t="n">
-        <v>1.2151</v>
+        <v>0.5074</v>
       </c>
       <c r="U23" t="n">
-        <v>0.156</v>
+        <v>0.1896</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>16.6758</v>
+        <v>17.462</v>
       </c>
       <c r="E24" t="n">
         <v>18.8951</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.2194</v>
+        <v>-1.4332</v>
       </c>
       <c r="G24" t="n">
         <v>4.8797</v>
@@ -2326,13 +2326,13 @@
         <v>4.639399999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>7.705300000000001</v>
+        <v>8.4918</v>
       </c>
       <c r="T24" t="n">
         <v>1.1817</v>
       </c>
       <c r="U24" t="n">
-        <v>6.5238</v>
+        <v>7.3101</v>
       </c>
       <c r="V24" t="n">
         <v>5.2503</v>
